--- a/DECEMBER/OUTSTANDING BAR/PANCA NIAGA BALI DECEMBER OUTSTANDING.xlsx
+++ b/DECEMBER/OUTSTANDING BAR/PANCA NIAGA BALI DECEMBER OUTSTANDING.xlsx
@@ -1147,45 +1147,6 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>46990</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>23495</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>4042410</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>2432685</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="ID_6FEA9A5BB26F4ABA9FAE8626885A024E" descr="PHOTO-2025-12-02-17-00-58"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:srcRect l="10286" t="816" r="1093" b="4776"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="5910580" y="226695"/>
-          <a:ext cx="3995420" cy="2409190"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>4</xdr:col>
       <xdr:colOff>56515</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>23495</xdr:rowOff>
@@ -1198,13 +1159,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="ID_8C956C0D3AE2463AA0AAE770DF7F3D09" descr="PHOTO-2025-12-31-22-28-18"/>
+        <xdr:cNvPr id="4" name="ID_8C956C0D3AE2463AA0AAE770DF7F3D09" descr="PHOTO-2025-12-31-22-28-18"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId2"/>
+        <a:blip r:embed="rId1"/>
         <a:srcRect t="4030" r="2764" b="9291"/>
         <a:stretch>
           <a:fillRect/>
@@ -1214,6 +1175,45 @@
         <a:xfrm rot="16200000">
           <a:off x="6654165" y="1931035"/>
           <a:ext cx="2507615" cy="3975735"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>135890</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>24130</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>3952875</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>2432685</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="ID_D3B37D0E933A4267A37A959164C79C4B" descr="PHOTO-2026-01-03-20-25-42"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId2"/>
+        <a:srcRect l="4382" t="12985" b="1616"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm rot="16200000">
+          <a:off x="6703695" y="-476885"/>
+          <a:ext cx="2408555" cy="3816985"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1483,7 +1483,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H174"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="16.8" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="17.4296875" style="1" customWidth="1"/>
@@ -1637,507 +1637,21 @@
         <v>4175000</v>
       </c>
     </row>
-    <row r="8" customFormat="1" ht="177" customHeight="1" spans="1:1">
-      <c r="A8" s="1"/>
-    </row>
-    <row r="9" customFormat="1" ht="177" customHeight="1" spans="1:1">
-      <c r="A9" s="1"/>
-    </row>
-    <row r="10" customFormat="1" ht="177" customHeight="1" spans="1:1">
-      <c r="A10" s="1"/>
-    </row>
-    <row r="11" customFormat="1" ht="177" customHeight="1" spans="1:1">
-      <c r="A11" s="1"/>
-    </row>
-    <row r="12" customFormat="1" ht="34" customHeight="1" spans="1:1">
-      <c r="A12" s="1"/>
-    </row>
-    <row r="13" customFormat="1" ht="58" customHeight="1" spans="1:1">
-      <c r="A13" s="1"/>
-    </row>
-    <row r="14" customFormat="1" ht="58" customHeight="1" spans="1:1">
-      <c r="A14" s="1"/>
-    </row>
-    <row r="15" customFormat="1" ht="58" customHeight="1" spans="1:1">
-      <c r="A15" s="1"/>
-    </row>
-    <row r="16" customFormat="1" ht="58" customHeight="1" spans="1:1">
-      <c r="A16" s="1"/>
-    </row>
-    <row r="17" customFormat="1" ht="58" customHeight="1" spans="1:1">
-      <c r="A17" s="1"/>
-    </row>
-    <row r="18" customFormat="1" ht="58" customHeight="1" spans="1:1">
-      <c r="A18" s="1"/>
-    </row>
-    <row r="19" customFormat="1" ht="58" customHeight="1" spans="1:1">
-      <c r="A19" s="1"/>
-    </row>
-    <row r="20" customFormat="1" ht="58" customHeight="1" spans="1:1">
-      <c r="A20" s="1"/>
-    </row>
-    <row r="21" customFormat="1" ht="58" customHeight="1" spans="1:1">
-      <c r="A21" s="1"/>
-    </row>
-    <row r="22" customFormat="1" ht="58" customHeight="1" spans="1:1">
-      <c r="A22" s="1"/>
-    </row>
-    <row r="23" customFormat="1" spans="1:1">
-      <c r="A23" s="1"/>
-    </row>
-    <row r="24" customFormat="1" spans="1:1">
-      <c r="A24" s="1"/>
-    </row>
-    <row r="25" customFormat="1" spans="1:1">
-      <c r="A25" s="1"/>
-    </row>
-    <row r="26" customFormat="1" spans="1:1">
-      <c r="A26" s="1"/>
-    </row>
-    <row r="27" customFormat="1" spans="1:1">
-      <c r="A27" s="1"/>
-    </row>
-    <row r="28" customFormat="1" spans="1:1">
-      <c r="A28" s="1"/>
-    </row>
-    <row r="29" customFormat="1" spans="1:1">
-      <c r="A29" s="1"/>
-    </row>
-    <row r="30" customFormat="1" spans="1:1">
-      <c r="A30" s="1"/>
-    </row>
-    <row r="31" customFormat="1" spans="1:1">
-      <c r="A31" s="1"/>
-    </row>
-    <row r="32" customFormat="1" spans="1:1">
-      <c r="A32" s="1"/>
-    </row>
-    <row r="33" customFormat="1" spans="1:1">
-      <c r="A33" s="1"/>
-    </row>
-    <row r="34" customFormat="1" spans="1:1">
-      <c r="A34" s="1"/>
-    </row>
-    <row r="35" customFormat="1" spans="1:1">
-      <c r="A35" s="1"/>
-    </row>
-    <row r="36" customFormat="1" spans="1:1">
-      <c r="A36" s="1"/>
-    </row>
-    <row r="37" customFormat="1" spans="1:1">
-      <c r="A37" s="1"/>
-    </row>
-    <row r="38" customFormat="1" spans="1:1">
-      <c r="A38" s="1"/>
-    </row>
-    <row r="39" customFormat="1" spans="1:1">
-      <c r="A39" s="1"/>
-    </row>
-    <row r="40" customFormat="1" spans="1:1">
-      <c r="A40" s="1"/>
-    </row>
-    <row r="41" customFormat="1" spans="1:1">
-      <c r="A41" s="1"/>
-    </row>
-    <row r="42" customFormat="1" spans="1:1">
-      <c r="A42" s="1"/>
-    </row>
-    <row r="43" customFormat="1" spans="1:1">
-      <c r="A43" s="1"/>
-    </row>
-    <row r="44" customFormat="1" spans="1:1">
-      <c r="A44" s="1"/>
-    </row>
-    <row r="45" customFormat="1" spans="1:1">
-      <c r="A45" s="1"/>
-    </row>
-    <row r="46" customFormat="1" spans="1:1">
-      <c r="A46" s="1"/>
-    </row>
-    <row r="47" customFormat="1" spans="1:1">
-      <c r="A47" s="1"/>
-    </row>
-    <row r="48" customFormat="1" spans="1:1">
-      <c r="A48" s="1"/>
-    </row>
-    <row r="49" customFormat="1" spans="1:1">
-      <c r="A49" s="1"/>
-    </row>
-    <row r="50" customFormat="1" spans="1:1">
-      <c r="A50" s="1"/>
-    </row>
-    <row r="51" customFormat="1" spans="1:1">
-      <c r="A51" s="1"/>
-    </row>
-    <row r="52" customFormat="1" spans="1:1">
-      <c r="A52" s="1"/>
-    </row>
-    <row r="53" customFormat="1" spans="1:1">
-      <c r="A53" s="1"/>
-    </row>
-    <row r="54" customFormat="1" spans="1:1">
-      <c r="A54" s="1"/>
-    </row>
-    <row r="55" customFormat="1" spans="1:1">
-      <c r="A55" s="1"/>
-    </row>
-    <row r="56" customFormat="1" spans="1:1">
-      <c r="A56" s="1"/>
-    </row>
-    <row r="57" customFormat="1" spans="1:1">
-      <c r="A57" s="1"/>
-    </row>
-    <row r="58" customFormat="1" spans="1:1">
-      <c r="A58" s="1"/>
-    </row>
-    <row r="59" customFormat="1" spans="1:1">
-      <c r="A59" s="1"/>
-    </row>
-    <row r="60" customFormat="1" spans="1:1">
-      <c r="A60" s="1"/>
-    </row>
-    <row r="61" customFormat="1" spans="1:1">
-      <c r="A61" s="1"/>
-    </row>
-    <row r="62" customFormat="1" spans="1:1">
-      <c r="A62" s="1"/>
-    </row>
-    <row r="63" customFormat="1" spans="1:1">
-      <c r="A63" s="1"/>
-    </row>
-    <row r="64" customFormat="1" spans="1:1">
-      <c r="A64" s="1"/>
-    </row>
-    <row r="65" customFormat="1" spans="1:1">
-      <c r="A65" s="1"/>
-    </row>
-    <row r="66" customFormat="1" spans="1:1">
-      <c r="A66" s="1"/>
-    </row>
-    <row r="67" customFormat="1" spans="1:1">
-      <c r="A67" s="1"/>
-    </row>
-    <row r="68" customFormat="1" spans="1:1">
-      <c r="A68" s="1"/>
-    </row>
-    <row r="69" customFormat="1" spans="1:1">
-      <c r="A69" s="1"/>
-    </row>
-    <row r="70" customFormat="1" spans="1:1">
-      <c r="A70" s="1"/>
-    </row>
-    <row r="71" customFormat="1" spans="1:1">
-      <c r="A71" s="1"/>
-    </row>
-    <row r="72" customFormat="1" spans="1:1">
-      <c r="A72" s="1"/>
-    </row>
-    <row r="73" customFormat="1" spans="1:1">
-      <c r="A73" s="1"/>
-    </row>
-    <row r="74" customFormat="1" spans="1:1">
-      <c r="A74" s="1"/>
-    </row>
-    <row r="75" customFormat="1" spans="1:1">
-      <c r="A75" s="1"/>
-    </row>
-    <row r="76" customFormat="1" spans="1:1">
-      <c r="A76" s="1"/>
-    </row>
-    <row r="77" customFormat="1" spans="1:1">
-      <c r="A77" s="1"/>
-    </row>
-    <row r="78" customFormat="1" spans="1:1">
-      <c r="A78" s="1"/>
-    </row>
-    <row r="79" customFormat="1" spans="1:1">
-      <c r="A79" s="1"/>
-    </row>
-    <row r="80" customFormat="1" spans="1:1">
-      <c r="A80" s="1"/>
-    </row>
-    <row r="81" customFormat="1" spans="1:1">
-      <c r="A81" s="1"/>
-    </row>
-    <row r="82" customFormat="1" spans="1:1">
-      <c r="A82" s="1"/>
-    </row>
-    <row r="83" customFormat="1" spans="1:1">
-      <c r="A83" s="1"/>
-    </row>
-    <row r="84" customFormat="1" spans="1:1">
-      <c r="A84" s="1"/>
-    </row>
-    <row r="85" customFormat="1" spans="1:1">
-      <c r="A85" s="1"/>
-    </row>
-    <row r="86" customFormat="1" spans="1:1">
-      <c r="A86" s="1"/>
-    </row>
-    <row r="87" customFormat="1" spans="1:1">
-      <c r="A87" s="1"/>
-    </row>
-    <row r="88" customFormat="1" spans="1:1">
-      <c r="A88" s="1"/>
-    </row>
-    <row r="89" customFormat="1" spans="1:1">
-      <c r="A89" s="1"/>
-    </row>
-    <row r="90" customFormat="1" spans="1:1">
-      <c r="A90" s="1"/>
-    </row>
-    <row r="91" customFormat="1" spans="1:1">
-      <c r="A91" s="1"/>
-    </row>
-    <row r="92" customFormat="1" spans="1:1">
-      <c r="A92" s="1"/>
-    </row>
-    <row r="93" customFormat="1" spans="1:1">
-      <c r="A93" s="1"/>
-    </row>
-    <row r="94" customFormat="1" spans="1:1">
-      <c r="A94" s="1"/>
-    </row>
-    <row r="95" customFormat="1" spans="1:1">
-      <c r="A95" s="1"/>
-    </row>
-    <row r="96" customFormat="1" spans="1:1">
-      <c r="A96" s="1"/>
-    </row>
-    <row r="97" customFormat="1" spans="1:1">
-      <c r="A97" s="1"/>
-    </row>
-    <row r="98" customFormat="1" spans="1:1">
-      <c r="A98" s="1"/>
-    </row>
-    <row r="99" customFormat="1" spans="1:1">
-      <c r="A99" s="1"/>
-    </row>
-    <row r="100" customFormat="1" spans="1:1">
-      <c r="A100" s="1"/>
-    </row>
-    <row r="101" customFormat="1" spans="1:1">
-      <c r="A101" s="1"/>
-    </row>
-    <row r="102" customFormat="1" spans="1:1">
-      <c r="A102" s="1"/>
-    </row>
-    <row r="103" customFormat="1" spans="1:1">
-      <c r="A103" s="1"/>
-    </row>
-    <row r="104" customFormat="1" spans="1:1">
-      <c r="A104" s="1"/>
-    </row>
-    <row r="105" customFormat="1" spans="1:1">
-      <c r="A105" s="1"/>
-    </row>
-    <row r="106" customFormat="1" spans="1:1">
-      <c r="A106" s="1"/>
-    </row>
-    <row r="107" customFormat="1" spans="1:1">
-      <c r="A107" s="1"/>
-    </row>
-    <row r="108" customFormat="1" spans="1:1">
-      <c r="A108" s="1"/>
-    </row>
-    <row r="109" customFormat="1" spans="1:1">
-      <c r="A109" s="1"/>
-    </row>
-    <row r="110" customFormat="1" spans="1:1">
-      <c r="A110" s="1"/>
-    </row>
-    <row r="111" customFormat="1" spans="1:1">
-      <c r="A111" s="1"/>
-    </row>
-    <row r="112" customFormat="1" spans="1:1">
-      <c r="A112" s="1"/>
-    </row>
-    <row r="113" customFormat="1" spans="1:1">
-      <c r="A113" s="1"/>
-    </row>
-    <row r="114" customFormat="1" spans="1:1">
-      <c r="A114" s="1"/>
-    </row>
-    <row r="115" customFormat="1" spans="1:1">
-      <c r="A115" s="1"/>
-    </row>
-    <row r="116" customFormat="1" spans="1:1">
-      <c r="A116" s="1"/>
-    </row>
-    <row r="117" customFormat="1" spans="1:1">
-      <c r="A117" s="1"/>
-    </row>
-    <row r="118" customFormat="1" spans="1:1">
-      <c r="A118" s="1"/>
-    </row>
-    <row r="119" customFormat="1" spans="1:1">
-      <c r="A119" s="1"/>
-    </row>
-    <row r="120" customFormat="1" spans="1:1">
-      <c r="A120" s="1"/>
-    </row>
-    <row r="121" customFormat="1" spans="1:1">
-      <c r="A121" s="1"/>
-    </row>
-    <row r="122" customFormat="1" spans="1:1">
-      <c r="A122" s="1"/>
-    </row>
-    <row r="123" customFormat="1" spans="1:1">
-      <c r="A123" s="1"/>
-    </row>
-    <row r="124" customFormat="1" spans="1:1">
-      <c r="A124" s="1"/>
-    </row>
-    <row r="125" customFormat="1" spans="1:1">
-      <c r="A125" s="1"/>
-    </row>
-    <row r="126" customFormat="1" spans="1:1">
-      <c r="A126" s="1"/>
-    </row>
-    <row r="127" customFormat="1" spans="1:1">
-      <c r="A127" s="1"/>
-    </row>
-    <row r="128" customFormat="1" spans="1:1">
-      <c r="A128" s="1"/>
-    </row>
-    <row r="129" customFormat="1" spans="1:1">
-      <c r="A129" s="1"/>
-    </row>
-    <row r="130" customFormat="1" spans="1:1">
-      <c r="A130" s="1"/>
-    </row>
-    <row r="131" customFormat="1" spans="1:1">
-      <c r="A131" s="1"/>
-    </row>
-    <row r="132" customFormat="1" spans="1:1">
-      <c r="A132" s="1"/>
-    </row>
-    <row r="133" customFormat="1" spans="1:1">
-      <c r="A133" s="1"/>
-    </row>
-    <row r="134" customFormat="1" spans="1:1">
-      <c r="A134" s="1"/>
-    </row>
-    <row r="135" customFormat="1" spans="1:1">
-      <c r="A135" s="1"/>
-    </row>
-    <row r="136" customFormat="1" spans="1:1">
-      <c r="A136" s="1"/>
-    </row>
-    <row r="137" customFormat="1" spans="1:1">
-      <c r="A137" s="1"/>
-    </row>
-    <row r="138" customFormat="1" spans="1:1">
-      <c r="A138" s="1"/>
-    </row>
-    <row r="139" customFormat="1" spans="1:1">
-      <c r="A139" s="1"/>
-    </row>
-    <row r="140" customFormat="1" spans="1:1">
-      <c r="A140" s="1"/>
-    </row>
-    <row r="141" customFormat="1" spans="1:1">
-      <c r="A141" s="1"/>
-    </row>
-    <row r="142" customFormat="1" spans="1:1">
-      <c r="A142" s="1"/>
-    </row>
-    <row r="143" customFormat="1" spans="1:1">
-      <c r="A143" s="1"/>
-    </row>
-    <row r="144" customFormat="1" spans="1:1">
-      <c r="A144" s="1"/>
-    </row>
-    <row r="145" customFormat="1" spans="1:1">
-      <c r="A145" s="1"/>
-    </row>
-    <row r="146" customFormat="1" spans="1:1">
-      <c r="A146" s="1"/>
-    </row>
-    <row r="147" customFormat="1" spans="1:1">
-      <c r="A147" s="1"/>
-    </row>
-    <row r="148" customFormat="1" spans="1:1">
-      <c r="A148" s="1"/>
-    </row>
-    <row r="149" customFormat="1" spans="1:1">
-      <c r="A149" s="1"/>
-    </row>
-    <row r="150" customFormat="1" spans="1:1">
-      <c r="A150" s="1"/>
-    </row>
-    <row r="151" customFormat="1" spans="1:1">
-      <c r="A151" s="1"/>
-    </row>
-    <row r="152" customFormat="1" spans="1:1">
-      <c r="A152" s="1"/>
-    </row>
-    <row r="153" customFormat="1" spans="1:1">
-      <c r="A153" s="1"/>
-    </row>
-    <row r="154" customFormat="1" spans="1:1">
-      <c r="A154" s="1"/>
-    </row>
-    <row r="155" customFormat="1" spans="1:1">
-      <c r="A155" s="1"/>
-    </row>
-    <row r="156" customFormat="1" spans="1:1">
-      <c r="A156" s="1"/>
-    </row>
-    <row r="157" customFormat="1" spans="1:1">
-      <c r="A157" s="1"/>
-    </row>
-    <row r="158" customFormat="1" spans="1:1">
-      <c r="A158" s="1"/>
-    </row>
-    <row r="159" customFormat="1" spans="1:1">
-      <c r="A159" s="1"/>
-    </row>
-    <row r="160" customFormat="1" spans="1:1">
-      <c r="A160" s="1"/>
-    </row>
-    <row r="161" customFormat="1" spans="1:1">
-      <c r="A161" s="1"/>
-    </row>
-    <row r="162" customFormat="1" spans="1:1">
-      <c r="A162" s="1"/>
-    </row>
-    <row r="163" customFormat="1" spans="1:1">
-      <c r="A163" s="1"/>
-    </row>
-    <row r="164" customFormat="1" spans="1:1">
-      <c r="A164" s="1"/>
-    </row>
-    <row r="165" customFormat="1" spans="1:1">
-      <c r="A165" s="1"/>
-    </row>
-    <row r="166" customFormat="1" spans="1:1">
-      <c r="A166" s="1"/>
-    </row>
-    <row r="167" customFormat="1" spans="1:1">
-      <c r="A167" s="1"/>
-    </row>
-    <row r="168" customFormat="1" spans="1:1">
-      <c r="A168" s="1"/>
-    </row>
-    <row r="169" customFormat="1" spans="1:1">
-      <c r="A169" s="1"/>
-    </row>
-    <row r="170" customFormat="1" spans="1:1">
-      <c r="A170" s="1"/>
-    </row>
-    <row r="171" customFormat="1" spans="1:1">
-      <c r="A171" s="1"/>
-    </row>
-    <row r="172" customFormat="1" spans="1:1">
-      <c r="A172" s="1"/>
-    </row>
-    <row r="173" customFormat="1" spans="1:1">
-      <c r="A173" s="1"/>
-    </row>
-    <row r="174" customFormat="1" spans="1:1">
-      <c r="A174" s="1"/>
-    </row>
+    <row r="8" ht="177" customHeight="1"/>
+    <row r="9" ht="177" customHeight="1"/>
+    <row r="10" ht="177" customHeight="1"/>
+    <row r="11" ht="177" customHeight="1"/>
+    <row r="12" ht="34" customHeight="1"/>
+    <row r="13" ht="58" customHeight="1"/>
+    <row r="14" ht="58" customHeight="1"/>
+    <row r="15" ht="58" customHeight="1"/>
+    <row r="16" ht="58" customHeight="1"/>
+    <row r="17" ht="58" customHeight="1"/>
+    <row r="18" ht="58" customHeight="1"/>
+    <row r="19" ht="58" customHeight="1"/>
+    <row r="20" ht="58" customHeight="1"/>
+    <row r="21" ht="58" customHeight="1"/>
+    <row r="22" ht="58" customHeight="1"/>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A7:C7"/>
